--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>57845</v>
+        <v>78840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,48 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R7" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532759</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>78840</v>
+        <v>57845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,34 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448012</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950940</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78840</v>
+        <v>57845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B13" t="n">
-        <v>57845</v>
+        <v>78840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B7" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R7" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1361,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B9" t="n">
-        <v>57845</v>
+        <v>78840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128532661</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128533482</v>
+        <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,42 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448088</v>
+        <v>448012</v>
       </c>
       <c r="R7" t="n">
-        <v>6950890</v>
+        <v>6950940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>57845</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,48 +1348,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R8" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532759</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>78840</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,34 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448012</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950940</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>57845</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R12" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>78840</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R13" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
         <v>128533563</v>
       </c>
       <c r="B14" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>128533692</v>
       </c>
       <c r="B15" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B4" t="n">
-        <v>92760</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R4" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,62 +994,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>92766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R5" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R7" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1361,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>78844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>78844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,42 +1241,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R7" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,48 +1362,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R8" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B9" t="n">
-        <v>78844</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,34 +1469,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R9" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>92768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R4" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,57 +984,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>92766</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R5" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,48 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R7" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,34 +1348,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R8" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,42 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R12" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>78844</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R13" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,19 +1999,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128533563</v>
+        <v>128533692</v>
       </c>
       <c r="B14" t="n">
         <v>57793</v>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448072</v>
+        <v>448076</v>
       </c>
       <c r="R14" t="n">
-        <v>6950905</v>
+        <v>6950900</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,19 +2115,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128533692</v>
+        <v>128533563</v>
       </c>
       <c r="B15" t="n">
         <v>57793</v>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448076</v>
+        <v>448072</v>
       </c>
       <c r="R15" t="n">
-        <v>6950900</v>
+        <v>6950905</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,12 +2231,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532759</v>
+        <v>128532655</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1241,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448012</v>
+        <v>447982</v>
       </c>
       <c r="R7" t="n">
-        <v>6950940</v>
+        <v>6950947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532759</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1362,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>448012</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1469,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128533692</v>
+        <v>128533563</v>
       </c>
       <c r="B14" t="n">
         <v>57793</v>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448076</v>
+        <v>448072</v>
       </c>
       <c r="R14" t="n">
-        <v>6950900</v>
+        <v>6950905</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,19 +2115,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128533563</v>
+        <v>128533692</v>
       </c>
       <c r="B15" t="n">
         <v>57793</v>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448072</v>
+        <v>448076</v>
       </c>
       <c r="R15" t="n">
-        <v>6950905</v>
+        <v>6950900</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,12 +2231,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,48 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R7" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,34 +1348,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R8" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,42 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128532661</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1348,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1469,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>78873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R12" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R13" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,22 +1999,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128533563</v>
+        <v>128533692</v>
       </c>
       <c r="B14" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448072</v>
+        <v>448076</v>
       </c>
       <c r="R14" t="n">
-        <v>6950905</v>
+        <v>6950900</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,22 +2115,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128533692</v>
+        <v>128533563</v>
       </c>
       <c r="B15" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448076</v>
+        <v>448072</v>
       </c>
       <c r="R15" t="n">
-        <v>6950900</v>
+        <v>6950905</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,12 +2231,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B4" t="n">
-        <v>92796</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R4" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,62 +994,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>92796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R5" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>92801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R4" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,57 +984,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>92796</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R5" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
         <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,48 +1348,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R8" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,42 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128533692</v>
+        <v>128533563</v>
       </c>
       <c r="B14" t="n">
         <v>57820</v>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448076</v>
+        <v>448072</v>
       </c>
       <c r="R14" t="n">
-        <v>6950900</v>
+        <v>6950905</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,19 +2115,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128533563</v>
+        <v>128533692</v>
       </c>
       <c r="B15" t="n">
         <v>57820</v>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448072</v>
+        <v>448076</v>
       </c>
       <c r="R15" t="n">
-        <v>6950905</v>
+        <v>6950900</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,12 +2231,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B4" t="n">
-        <v>92801</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R4" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,62 +994,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>92806</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R5" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1348,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1469,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>92806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R4" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,57 +984,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>92806</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R5" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,48 +1348,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R8" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,42 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78877</v>
+        <v>57876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>78877</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B4" t="n">
-        <v>92806</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R4" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,62 +994,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>92810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R5" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>128532661</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>57876</v>
+        <v>78881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R12" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>78877</v>
+        <v>57880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R13" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
         <v>128533563</v>
       </c>
       <c r="B14" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>128533692</v>
       </c>
       <c r="B15" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532761</v>
+        <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>92810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447983</v>
+        <v>448042</v>
       </c>
       <c r="R4" t="n">
-        <v>6950981</v>
+        <v>6950931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,57 +984,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532860</v>
+        <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>92810</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448042</v>
+        <v>447983</v>
       </c>
       <c r="R5" t="n">
-        <v>6950931</v>
+        <v>6950981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1348,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B9" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1469,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>57880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B13" t="n">
-        <v>57880</v>
+        <v>78881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B8" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,48 +1348,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R8" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1425,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1445,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,42 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>57880</v>
+        <v>78881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R12" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>78881</v>
+        <v>57880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R13" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128532761</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128532661</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R7" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1361,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R8" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,12 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B9" t="n">
-        <v>57880</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>128533563</v>
       </c>
       <c r="B14" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>128533692</v>
       </c>
       <c r="B15" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128532759</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>78791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1915,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532759</v>
+        <v>128533482</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448012</v>
+        <v>448088</v>
       </c>
       <c r="R7" t="n">
-        <v>6950940</v>
+        <v>6950890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1338,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532655</v>
+        <v>128532759</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,48 +1361,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447982</v>
+        <v>448012</v>
       </c>
       <c r="R8" t="n">
-        <v>6950947</v>
+        <v>6950940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,42 +1468,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128532233</v>
+        <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>78791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447903</v>
+        <v>448028</v>
       </c>
       <c r="R12" t="n">
-        <v>6951077</v>
+        <v>6950948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B13" t="n">
-        <v>78791</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R13" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,12 +1999,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128533328</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128533330</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128532860</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128533482</v>
+        <v>128532655</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,42 +1241,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448088</v>
+        <v>447982</v>
       </c>
       <c r="R7" t="n">
-        <v>6950890</v>
+        <v>6950947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,12 +1339,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1353,7 +1354,7 @@
         <v>128532759</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128532655</v>
+        <v>128533482</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,48 +1469,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447982</v>
+        <v>448088</v>
       </c>
       <c r="R9" t="n">
-        <v>6950947</v>
+        <v>6950890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1546,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>128533002</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128533476</v>
       </c>
       <c r="B11" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128533120</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19530-2025 artfynd.xlsx
+++ b/artfynd/A 19530-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128533328</v>
+        <v>128532860</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448045</v>
+        <v>448042</v>
       </c>
       <c r="R2" t="n">
-        <v>6950937</v>
+        <v>6950931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128533330</v>
+        <v>128533002</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448040</v>
+        <v>448054</v>
       </c>
       <c r="R3" t="n">
-        <v>6950958</v>
+        <v>6950942</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,26 +877,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532860</v>
+        <v>128533476</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448042</v>
+        <v>448088</v>
       </c>
       <c r="R4" t="n">
-        <v>6950931</v>
+        <v>6950890</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532761</v>
+        <v>128532759</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447983</v>
+        <v>448012</v>
       </c>
       <c r="R5" t="n">
-        <v>6950981</v>
+        <v>6950940</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,11 +1079,6 @@
           <t>10:19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1101,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532661</v>
+        <v>128533120</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447969</v>
+        <v>448028</v>
       </c>
       <c r="R6" t="n">
-        <v>6951011</v>
+        <v>6950948</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532655</v>
+        <v>128533328</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,48 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
+          <t>Vällströmmen, Vällströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447982</v>
+        <v>448045</v>
       </c>
       <c r="R7" t="n">
-        <v>6950947</v>
+        <v>6950937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128532759</v>
+        <v>128533330</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448012</v>
+        <v>448040</v>
       </c>
       <c r="R8" t="n">
-        <v>6950940</v>
+        <v>6950958</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533482</v>
+        <v>128532661</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,27 +1453,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448088</v>
+        <v>447969</v>
       </c>
       <c r="R9" t="n">
-        <v>6950890</v>
+        <v>6951011</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,12 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,45 +1541,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128533002</v>
+        <v>128532761</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448054</v>
+        <v>447983</v>
       </c>
       <c r="R10" t="n">
-        <v>6950942</v>
+        <v>6950981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1626,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,50 +1646,58 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128533476</v>
+        <v>128533482</v>
       </c>
       <c r="B11" t="n">
-        <v>92831</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1726,7 +1707,7 @@
         <v>6950890</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1746,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533120</v>
+        <v>128532233</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1789,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vällströmmen, Vällströmmen, Jmt</t>
+          <t>Vällströmmen, Ljungan, Klövsjö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448028</v>
+        <v>447903</v>
       </c>
       <c r="R12" t="n">
-        <v>6950948</v>
+        <v>6951077</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1878,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128532233</v>
+        <v>128532655</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,10 +1918,19 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447903</v>
+        <v>447982</v>
       </c>
       <c r="R13" t="n">
-        <v>6951077</v>
+        <v>6950947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,11 +2014,11 @@
         <v>128533563</v>
       </c>
       <c r="B14" t="n">
-        <v>57827</v>
+        <v>58057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2130,11 +2130,11 @@
         <v>128533692</v>
       </c>
       <c r="B15" t="n">
-        <v>57827</v>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
